--- a/_posts/工作簿1.xlsx
+++ b/_posts/工作簿1.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mxm\Documents\Code\blog\_posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CDB87ED2-8290-4BAE-AB3E-2669758E4241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E186644-BCD9-4822-A425-28E59ECDCEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{5772B7EC-0D34-4D98-8C50-8053F9C4DDDF}"/>
+    <workbookView xWindow="10800" yWindow="0" windowWidth="10800" windowHeight="13954" xr2:uid="{5772B7EC-0D34-4D98-8C50-8053F9C4DDDF}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作簿1" sheetId="1" r:id="rId1"/>
+    <sheet name="LeggedRobotCfgPPO" sheetId="3" r:id="rId1"/>
+    <sheet name="LeggedRobotCfg" sheetId="2" r:id="rId2"/>
+    <sheet name="BaseTask" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
   <si>
     <t>函数名/代码块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,6 +154,208 @@
   <si>
     <t>`self.fetch_results(self.sim, True)`来获取GPU计算结果，`self.gym.step_graphics(self.sim)`来渲染画面 
 self.gym.sync_frame_time(self.sim)是干嘛的？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class env`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定义环境基础参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>num_envs, num_observations, num_actions等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class terrain`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定义地形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mesh_type='trimesh' or `plane` or 'none`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class commands`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制指令相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>num_commands控制指令数，resampling_time控制指令改变周期，ranges指令的范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class init_state`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机器人初始位姿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class control`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PID相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P=stiffness; D=damping;
+action_scale表示将输出关节角度会乘以一个比例（作用是平滑，但是原理没懂？）
+decimation: 仿真环境时间dt * decimation = 控制指令下发时间周期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class asset`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机器人资产（模型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class domain_rand`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>域随机化定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于添加机器人环境中的扰动，模拟真实世界中的随机扰动，加强机器人的稳定性和鲁棒性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class rewards`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励函数定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class scales`每一项都对应一个reward函数，函数return * scale = reward value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class normalization`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归一化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class obs_scales定义obs的归一化参数（目的是让模型输入维度一致，稳定训练）
+clip_xxx则是限定数值范围[-clip, clip]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class noise`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加噪声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class viewer`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摄像头视角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class sim`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仿真环境参数定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dt 时间
+up_axis = 1,0代表y，1代表z（机器人默认是z）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`seed = 1`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机种子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`runner_class_name = 'OnPolicyRunner`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>算法类名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class policy`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定义神经网络模型参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>init_noise_std: 参数初始化std
+hidden_dims： MLP维度
+activation: 激活函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class algorithm`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练网络参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>learning_rate, num_learning_epochs, num_mini_batches等，具体要结合看PPO算法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`class runner`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运行过程的参数定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后续用eval(name)来得到类名var, 然后var()实例化
+详见`rsl_rl/runners/on_policy_runner.py`, 定义了整个算法训练过程、log、保存等的类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>算法之间的关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_iterations, save_interval, load_run, checkpoint等
+policy_class_name=PPO， algorithm_class_name=ActorCritic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnPolicyRunner定义了整个训练过程，包含learn, log, save等过程
+PPO为训练模型的一种方法
+ActorCritic应该是强化学习方法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -198,12 +402,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,22 +745,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50328ED3-D70A-43B4-9611-5AD33549D9AB}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="84.9" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="42.45" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="42.45" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="56.6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="56.6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EC9D5E-E984-42F1-9294-81606E8BCB14}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="61.35546875" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="27.45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="28.3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="56.6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="28.3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="42.45" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="28.3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5FA566-A393-4223-98D0-56D6655EFC9C}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="54.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="87.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="54.35546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="87.85546875" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,7 +1007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="42.45" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -575,7 +1018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -586,7 +1029,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="56.6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -597,7 +1040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="56.6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -608,7 +1051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="28.3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -619,7 +1062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="42.45" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -630,7 +1073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="42.45" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -641,7 +1084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="28.3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>

--- a/_posts/工作簿1.xlsx
+++ b/_posts/工作簿1.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mxm\Documents\Code\blog\_posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E186644-BCD9-4822-A425-28E59ECDCEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75621E4-0868-4B15-B1A0-FE58A875357B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10800" yWindow="0" windowWidth="10800" windowHeight="13954" xr2:uid="{5772B7EC-0D34-4D98-8C50-8053F9C4DDDF}"/>
+    <workbookView xWindow="-69" yWindow="-69" windowWidth="16595" windowHeight="12035" xr2:uid="{5772B7EC-0D34-4D98-8C50-8053F9C4DDDF}"/>
   </bookViews>
   <sheets>
-    <sheet name="LeggedRobotCfgPPO" sheetId="3" r:id="rId1"/>
-    <sheet name="LeggedRobotCfg" sheetId="2" r:id="rId2"/>
-    <sheet name="BaseTask" sheetId="1" r:id="rId3"/>
+    <sheet name="LeggedRobot" sheetId="4" r:id="rId1"/>
+    <sheet name="LeggedRobotCfgPPO" sheetId="3" r:id="rId2"/>
+    <sheet name="LeggedRobotCfg" sheetId="2" r:id="rId3"/>
+    <sheet name="BaseTask" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="77">
   <si>
     <t>函数名/代码块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -356,6 +357,49 @@
     <t>OnPolicyRunner定义了整个训练过程，包含learn, log, save等过程
 PPO为训练模型的一种方法
 ActorCritic应该是强化学习方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`__init__(self, cfg, …)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化类的属性
+设置viewer-camera
+映射reward scale-function</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">`self._parse_cfg(cfg)`:
+self.dt = decimation*dt # 所以env中的dt就是控制器输出的时间间隔，不是仿真环境的时间间隔
+self.max_episode_length = episode_length_s / dt # 也就是离散时间的采样点n
+self.cfg.domain_rand.push_interval: 同上
+所以**env中的时间概念都是离散时间的采样点n，离散时间的周期是仿真周期*decimation**
+`super().__init__()`:
+self.num_envs/num_obs/num_priviledge_obs/num_actions都有cfg中定义而来
+self.obs_buf: shape = (num_envs, num_obs,) 自定义obs维度
+self.rew_buf: shape = (num_envs,) 每个环境都有一个reward value记录
+self.reset_buf: shape = (num_envs, ) 每个环境一个reset flag True/False
+self.episode_length_buf: shape = (num, envs,) 记录当前trial/episode经过的时刻n
+self.time_out_buf: shape = (num_envs, )应该是存放一个最大时间来判断
+self.create_sim(): 在BaseTask中调用，但是在LeggedRobot中定义。
+`self.create_sim()`:
+self.up_axis_idx = 2 # 2 for z, 1 for y, 设置重力方向
+self._create_envs()
+`self._create_envs()`:
+加载assets
+self.dof_names: list of str，从asset文件中获取
+self.num_dofs # len(self.dof_names)，应该 == cfg.num_actions
+self.base_init_state: 加载由cfg中定义的init_state.pos/rot/lin_vel/ang_vel
+定义envs/actors，并且保存handle(引用) -&gt; self.envs / self.actor_handles: list of handle
+self.feet_indices / self.penalised_contact_indices / self.termination_contact_indices: 根据cfg.asset.foot_name等，根据self.gym.find_actor_rigid_body_handle(self.envs[0], self.actor_handles[0], feet_name[i])来获取索引
+`self._init_buffers()`: 从仿真gym中获取各种状态，建立其引用。则当self.gym.acquire/refresh时，对应的tensor就会自动更新，
+self.root_states: shape= (num_envs, 13) # 13=3pos+4rot+3lin_vel+3ang_vel
+self.dof_state: shape=(num_envs * num_actions, 2) # 2 = 位置与速度
+self.dof_pos: shape = (num_envs, num_actions)
+self.dof_vel: shape = (num_envs, num_actions)
+self.base_quat: shape = (num_envs, 4) # root坐标系相对世界坐标系的旋转四元数
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -745,6 +789,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B5FDB5-7724-4DBB-942F-4DB53D5A0685}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.0703125" customWidth="1"/>
+    <col min="2" max="2" width="26.2109375" customWidth="1"/>
+    <col min="3" max="3" width="79.5" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.35546875" customWidth="1"/>
+    <col min="6" max="6" width="42.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="42.45" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="409.6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50328ED3-D70A-43B4-9611-5AD33549D9AB}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
@@ -832,7 +917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EC9D5E-E984-42F1-9294-81606E8BCB14}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
@@ -980,7 +1065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5FA566-A393-4223-98D0-56D6655EFC9C}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
